--- a/output/pdf_financials_xlsx/FEO.xlsx
+++ b/output/pdf_financials_xlsx/FEO.xlsx
@@ -5394,19 +5394,19 @@
         <v>0</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>11.205166</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>11.243969</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>11.334926</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>11.465192</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>37.770279</v>
       </c>
     </row>
     <row r="93">
@@ -8981,7 +8981,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -12970,7 +12974,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FEO.xlsx
+++ b/output/pdf_financials_xlsx/FEO.xlsx
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000399</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.059159</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.116218</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.041558</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.083718</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.019255</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1835,22 +1835,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.253738</v>
+        <v>-0.254137</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.360868</v>
+        <v>-5.420027</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.284451</v>
+        <v>-3.400669</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.142516</v>
+        <v>-3.184074</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.058482</v>
+        <v>-3.1422</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.547528</v>
+        <v>-2.566783</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-1.865043</v>
@@ -1941,22 +1941,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.253738</v>
+        <v>-0.254137</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.360868</v>
+        <v>-5.420027</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.284451</v>
+        <v>-3.400669</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.142516</v>
+        <v>-3.184074</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.058482</v>
+        <v>-3.1422</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.547528</v>
+        <v>-2.566783</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-1.865043</v>
@@ -2250,19 +2250,19 @@
         <v>0.422788</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.293162</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.662818</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.269513</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.420984</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.9182090000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2354,19 +2354,19 @@
         <v>0.422788</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.293162</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.662818</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.269513</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.420984</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.9182090000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2978,19 +2978,19 @@
         <v>0.005903</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.306775</v>
+        <v>0.013613</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.669794</v>
+        <v>0.006976</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.283065</v>
+        <v>0.013552</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.423041</v>
+        <v>0.002057</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.92226</v>
+        <v>0.004051</v>
       </c>
     </row>
     <row r="49">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -51559,7 +51559,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -54639,7 +54639,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E528" s="5" t="n">

--- a/output/pdf_financials_xlsx/FEO.xlsx
+++ b/output/pdf_financials_xlsx/FEO.xlsx
@@ -716,46 +716,46 @@
         <v>0.110169</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.167429</v>
+        <v>0.174929</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.385015</v>
+        <v>0.436748</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.274269</v>
+        <v>0.311269</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.796789</v>
+        <v>0.832789</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.631588</v>
+        <v>0.661588</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.315494</v>
+        <v>0.345494</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.239375</v>
+        <v>0.269375</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.218281</v>
+        <v>0.235781</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.299252</v>
+        <v>0.324252</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.265099</v>
+        <v>0.295099</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.273602</v>
+        <v>0.303602</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.33114</v>
+        <v>0.36114</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.363294</v>
+        <v>0.393294</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.382426</v>
+        <v>0.402926</v>
       </c>
     </row>
     <row r="8">
@@ -875,19 +875,19 @@
         <v>5.488878</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.385015</v>
+        <v>0.436748</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.274269</v>
+        <v>0.311269</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.796789</v>
+        <v>0.832789</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.631588</v>
+        <v>0.661588</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.315494</v>
+        <v>0.345494</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.011828</v>
@@ -899,19 +899,19 @@
         <v>0.718654</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.265099</v>
+        <v>0.295099</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.273602</v>
+        <v>0.303602</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.33114</v>
+        <v>0.36114</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.363294</v>
+        <v>0.393294</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.382426</v>
+        <v>0.402926</v>
       </c>
     </row>
     <row r="11">
@@ -1238,22 +1238,22 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.14514</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-1.664146</v>
+        <v>1.664146</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.514193</v>
+        <v>-0.514193</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.652525</v>
+        <v>-0.652525</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.246758</v>
+        <v>-0.246758</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.12502</v>
+        <v>-0.12502</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -2080,7 +2080,7 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.707397384154954</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-50.66740225383176</v>
@@ -6303,19 +6303,19 @@
         <v>0</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.360463</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.454455</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.539281</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.69823</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.838412</v>
       </c>
     </row>
     <row r="111">
@@ -6533,19 +6533,19 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.010561</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.025726</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.171962</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.056114</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -22389,7 +22389,11 @@
           <t>Convertible debenture accretion expense 6</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -25948,7 +25952,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -26217,7 +26225,11 @@
           <t>Convertible debenture accretion expense 5</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -32010,7 +32022,11 @@
           <t>Deferred income tax (recovery)</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -34763,7 +34779,11 @@
           <t>Net proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -37441,7 +37461,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E336" s="5" t="n">
         <v>0.010561</v>
       </c>
@@ -38343,7 +38367,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -39259,7 +39287,11 @@
           <t>Private placements (Note 11(b))</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -39797,7 +39829,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -40711,7 +40747,11 @@
           <t>Private placements (Note 6(b))</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -41257,7 +41297,11 @@
           <t>Directors' fees 10</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -44203,7 +44247,11 @@
           <t>Directors' fees 9</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -47779,7 +47827,11 @@
           <t>Directors' fees</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
           <t>-</t>
@@ -48651,7 +48703,11 @@
           <t>Directors' fees 17,500</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -51110,7 +51166,11 @@
           <t>Deferred income tax recovery (Note 9)</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E489" t="inlineStr">
         <is>
           <t>-</t>
@@ -51468,7 +51528,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
@@ -52451,7 +52515,11 @@
           <t>Deferred income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E504" t="inlineStr">
         <is>
           <t>-</t>
@@ -52993,7 +53061,11 @@
           <t>Deferred income tax recovery/(expense) (Note 10)</t>
         </is>
       </c>
-      <c r="D510" t="inlineStr"/>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E510" t="inlineStr">
         <is>
           <t>-</t>
@@ -53264,7 +53336,11 @@
           <t>Directors Fees</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr">
         <is>
           <t>-</t>
@@ -55183,7 +55259,11 @@
           <t>Income tax recovery (Note 7)</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr">
         <is>
           <t>-</t>
